--- a/program/tab5.xlsx
+++ b/program/tab5.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,17 +10,17 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E14A13-448C-4439-B8DA-05723D42920C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="2970" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="2970" windowWidth="28800" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="88" uniqueCount="8">
   <si>
     <t>w1</t>
   </si>
@@ -49,11 +49,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -74,7 +74,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -84,53 +84,55 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -149,7 +151,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
@@ -300,7 +302,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -324,9 +326,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -350,7 +352,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -385,7 +387,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -403,7 +405,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -428,7 +430,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -464,20 +466,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="7" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="2" customWidth="true"/>
+    <col min="2" max="2" width="4.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="7.140625" style="1" customWidth="true"/>
+    <col min="4" max="4" width="5.140625" style="1" customWidth="true"/>
+    <col min="5" max="5" width="7.140625" style="1" customWidth="true"/>
+    <col min="6" max="6" width="7" style="1" customWidth="true"/>
+    <col min="8" max="8" width="6.7109375" style="4" customWidth="true"/>
+    <col min="7" max="7" width="7" style="1" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" s="3" customFormat="true" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -503,160 +506,160 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>2.5</v>
       </c>
       <c r="B2" s="9">
-        <v>431.59795252960487</v>
+        <v>428.91108665444909</v>
       </c>
       <c r="C2" s="9">
-        <v>265967.34772368631</v>
+        <v>265291.05477820878</v>
       </c>
       <c r="D2" s="9">
-        <v>4822.3758661819138</v>
+        <v>4822.0498435741065</v>
       </c>
       <c r="E2" s="9">
-        <v>101143.38304133026</v>
+        <v>101136.54511943935</v>
       </c>
       <c r="F2" s="9">
-        <v>18650.921991806797</v>
+        <v>18646.819907509853</v>
       </c>
       <c r="G2" s="9">
-        <v>24557.53334444635</v>
+        <v>24556.371163244636</v>
       </c>
       <c r="H2" s="10">
-        <v>6250.8799073511</v>
+        <v>6251.3025342908031</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>3</v>
       </c>
       <c r="B3" s="9">
-        <v>499.37221268631208</v>
+        <v>496.26342556300932</v>
       </c>
       <c r="C3" s="9">
-        <v>319160.81726842356</v>
+        <v>318349.26573385048</v>
       </c>
       <c r="D3" s="9">
-        <v>5032.5359691365102</v>
+        <v>5032.2283744160486</v>
       </c>
       <c r="E3" s="9">
-        <v>105551.23186584997</v>
+        <v>105544.78044615635</v>
       </c>
       <c r="F3" s="9">
-        <v>21579.695012685435</v>
+        <v>21574.948773969554</v>
       </c>
       <c r="G3" s="9">
-        <v>25301.881866713633</v>
+        <v>25300.799319529051</v>
       </c>
       <c r="H3" s="10">
-        <v>5989.841422391969</v>
+        <v>5990.2075511645217</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>3.5</v>
       </c>
       <c r="B4" s="9">
-        <v>564.9133060548761</v>
+        <v>561.39650001915652</v>
       </c>
       <c r="C4" s="9">
-        <v>372354.28681316081</v>
+        <v>371407.47668949224</v>
       </c>
       <c r="D4" s="9">
-        <v>5200.3300747375024</v>
+        <v>5200.0391996721883</v>
       </c>
       <c r="E4" s="9">
-        <v>109070.50617499159</v>
+        <v>109064.40542943284</v>
       </c>
       <c r="F4" s="9">
-        <v>24411.964750088708</v>
+        <v>24406.595581888712</v>
       </c>
       <c r="G4" s="9">
-        <v>25889.498588387778</v>
+        <v>25888.48490831977</v>
       </c>
       <c r="H4" s="10">
-        <v>5796.572904871422</v>
+        <v>5796.89714829682</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="9">
-        <v>628.60142597979848</v>
+        <v>624.68813651528581</v>
       </c>
       <c r="C5" s="9">
-        <v>425547.75635789812</v>
+        <v>424465.68764513405</v>
       </c>
       <c r="D5" s="9">
-        <v>5337.9481987523777</v>
+        <v>5337.6723694806287</v>
       </c>
       <c r="E5" s="9">
-        <v>111956.87650715034</v>
+        <v>111951.0913285453</v>
       </c>
       <c r="F5" s="9">
-        <v>27164.160745372268</v>
+        <v>27158.186259109225</v>
       </c>
       <c r="G5" s="9">
-        <v>26367.202271841168</v>
+        <v>26366.248528640215</v>
       </c>
       <c r="H5" s="10">
-        <v>5647.1309359384322</v>
+        <v>5647.422756774502</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>4.5</v>
       </c>
       <c r="B6" s="9">
-        <v>690.71260213827657</v>
+        <v>686.41264633601156</v>
       </c>
       <c r="C6" s="9">
-        <v>478741.22590263537</v>
+        <v>477523.89860077581</v>
       </c>
       <c r="D6" s="9">
-        <v>5453.2073660720889</v>
+        <v>5452.945064202584</v>
       </c>
       <c r="E6" s="9">
-        <v>114374.29531330247</v>
+        <v>114368.79385526685</v>
       </c>
       <c r="F6" s="9">
-        <v>29848.211247840034</v>
+        <v>29841.646431435493</v>
       </c>
       <c r="G6" s="9">
-        <v>26764.455425273241</v>
+        <v>26763.554250640849</v>
       </c>
       <c r="H6" s="10">
-        <v>5527.7729937719178</v>
+        <v>5528.0388950735805</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>5</v>
       </c>
       <c r="B7" s="9">
-        <v>751.45568138420276</v>
+        <v>746.77757618196665</v>
       </c>
       <c r="C7" s="9">
-        <v>531934.69544737262</v>
+        <v>530582.10955641756</v>
       </c>
       <c r="D7" s="9">
-        <v>5551.3788873954472</v>
+        <v>5551.1287742304612</v>
       </c>
       <c r="E7" s="9">
-        <v>116433.32183062371</v>
+        <v>116428.07601562467</v>
       </c>
       <c r="F7" s="9">
-        <v>32473.141291918957</v>
+        <v>32465.999148328166</v>
       </c>
       <c r="G7" s="9">
-        <v>27100.831186219977</v>
+        <v>27099.97647526869</v>
       </c>
       <c r="H7" s="10">
-        <v>5430.0189230560973</v>
+        <v>5430.2635794627522</v>
       </c>
     </row>
   </sheetData>

--- a/program/tab5.xlsx
+++ b/program/tab5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="88" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="104" uniqueCount="8">
   <si>
     <t>w1</t>
   </si>
@@ -511,25 +511,25 @@
         <v>2.5</v>
       </c>
       <c r="B2" s="9">
-        <v>428.91108665444909</v>
+        <v>431.59795252960487</v>
       </c>
       <c r="C2" s="9">
-        <v>265291.05477820878</v>
+        <v>265967.34772368631</v>
       </c>
       <c r="D2" s="9">
-        <v>4822.0498435741065</v>
+        <v>4740.8875632297768</v>
       </c>
       <c r="E2" s="9">
-        <v>101136.54511943935</v>
+        <v>99434.266442461434</v>
       </c>
       <c r="F2" s="9">
-        <v>18646.819907509853</v>
+        <v>18650.921991806797</v>
       </c>
       <c r="G2" s="9">
-        <v>24556.371163244636</v>
+        <v>24266.311110830855</v>
       </c>
       <c r="H2" s="10">
-        <v>6251.3025342908031</v>
+        <v>6358.3225726356232</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
@@ -537,25 +537,25 @@
         <v>3</v>
       </c>
       <c r="B3" s="9">
-        <v>496.26342556300932</v>
+        <v>499.37221268631208</v>
       </c>
       <c r="C3" s="9">
-        <v>318349.26573385048</v>
+        <v>319160.81726842356</v>
       </c>
       <c r="D3" s="9">
-        <v>5032.2283744160486</v>
+        <v>4943.6529201512321</v>
       </c>
       <c r="E3" s="9">
-        <v>105544.78044615635</v>
+        <v>103687.01959396063</v>
       </c>
       <c r="F3" s="9">
-        <v>21574.948773969554</v>
+        <v>21579.695012685435</v>
       </c>
       <c r="G3" s="9">
-        <v>25300.799319529051</v>
+        <v>24988.235091356775</v>
       </c>
       <c r="H3" s="10">
-        <v>5990.2075511645217</v>
+        <v>6097.5341300232785</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
@@ -563,25 +563,25 @@
         <v>3.5</v>
       </c>
       <c r="B4" s="9">
-        <v>561.39650001915652</v>
+        <v>564.9133060548761</v>
       </c>
       <c r="C4" s="9">
-        <v>371407.47668949224</v>
+        <v>372354.28681316081</v>
       </c>
       <c r="D4" s="9">
-        <v>5200.0391996721883</v>
+        <v>5105.3085685765436</v>
       </c>
       <c r="E4" s="9">
-        <v>109064.40542943284</v>
+        <v>107077.54733862216</v>
       </c>
       <c r="F4" s="9">
-        <v>24406.595581888712</v>
+        <v>24411.964750088708</v>
       </c>
       <c r="G4" s="9">
-        <v>25888.48490831977</v>
+        <v>25557.442935534516</v>
       </c>
       <c r="H4" s="10">
-        <v>5796.89714829682</v>
+        <v>5904.4604263785213</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
@@ -589,25 +589,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="9">
-        <v>624.68813651528581</v>
+        <v>628.60142597979848</v>
       </c>
       <c r="C5" s="9">
-        <v>424465.68764513405</v>
+        <v>425547.75635789812</v>
       </c>
       <c r="D5" s="9">
-        <v>5337.6723694806287</v>
+        <v>5237.7367007334751</v>
       </c>
       <c r="E5" s="9">
-        <v>111951.0913285453</v>
+        <v>109855.06399594594</v>
       </c>
       <c r="F5" s="9">
-        <v>27158.186259109225</v>
+        <v>27164.160745372268</v>
       </c>
       <c r="G5" s="9">
-        <v>26366.248528640215</v>
+        <v>26019.716857954099</v>
       </c>
       <c r="H5" s="10">
-        <v>5647.422756774502</v>
+        <v>5755.1752082898902</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
@@ -615,25 +615,25 @@
         <v>4.5</v>
       </c>
       <c r="B6" s="9">
-        <v>686.41264633601156</v>
+        <v>690.71260213827657</v>
       </c>
       <c r="C6" s="9">
-        <v>477523.89860077581</v>
+        <v>478741.22590263537</v>
       </c>
       <c r="D6" s="9">
-        <v>5452.945064202584</v>
+        <v>5348.5412265871974</v>
       </c>
       <c r="E6" s="9">
-        <v>114368.79385526685</v>
+        <v>112179.05219432111</v>
       </c>
       <c r="F6" s="9">
-        <v>29841.646431435493</v>
+        <v>29848.211247840034</v>
       </c>
       <c r="G6" s="9">
-        <v>26763.554250640849</v>
+        <v>26403.818926505464</v>
       </c>
       <c r="H6" s="10">
-        <v>5528.0388950735805</v>
+        <v>5635.9465376778535</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
@@ -641,25 +641,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="9">
-        <v>746.77757618196665</v>
+        <v>751.45568138420276</v>
       </c>
       <c r="C7" s="9">
-        <v>530582.10955641756</v>
+        <v>531934.69544737262</v>
       </c>
       <c r="D7" s="9">
-        <v>5551.1287742304612</v>
+        <v>5442.8409445762891</v>
       </c>
       <c r="E7" s="9">
-        <v>116428.07601562467</v>
+        <v>114156.87241446326</v>
       </c>
       <c r="F7" s="9">
-        <v>32465.999148328166</v>
+        <v>32473.141291918957</v>
       </c>
       <c r="G7" s="9">
-        <v>27099.97647526869</v>
+        <v>26728.830232442811</v>
       </c>
       <c r="H7" s="10">
-        <v>5430.2635794627522</v>
+        <v>5538.3011766400277</v>
       </c>
     </row>
   </sheetData>

--- a/program/tab5.xlsx
+++ b/program/tab5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="104" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="8">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab5.xlsx
+++ b/program/tab5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="120" uniqueCount="8">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab5.xlsx
+++ b/program/tab5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="120" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="128" uniqueCount="8">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab5.xlsx
+++ b/program/tab5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="128" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="136" uniqueCount="8">
   <si>
     <t>w1</t>
   </si>
